--- a/unit6_debugkernel/unit6_debugkernel.xlsx
+++ b/unit6_debugkernel/unit6_debugkernel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E2B0E4D-B40A-47B3-BFDF-9DBA0BE7B2A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025C2717-FC52-4BC1-A7A9-4037A1D7F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="5" r:id="rId1"/>
@@ -3590,6 +3590,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3599,9 +3602,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5590,33 +5590,33 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A553DCEE-A8AF-4E33-86F9-F082A764823C}">
   <dimension ref="B2:B10"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="16384" width="8.796875" style="44"/>
+    <col min="1" max="16384" width="8.75" style="41"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
-      <c r="B2" s="45" t="s">
+      <c r="B2" s="42" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="4" spans="2:2">
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="43" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="6" spans="2:2">
-      <c r="B6" s="46" t="s">
+      <c r="B6" s="43" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="8" spans="2:2">
-      <c r="B8" s="46" t="s">
+      <c r="B8" s="43" t="s">
         <v>198</v>
       </c>
     </row>
     <row r="10" spans="2:2">
-      <c r="B10" s="46" t="s">
+      <c r="B10" s="43" t="s">
         <v>199</v>
       </c>
     </row>
@@ -5635,29 +5635,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y57"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:25" ht="22.8">
+    <row r="1" spans="1:25" ht="23.25">
       <c r="A1" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="17.399999999999999">
+    <row r="2" spans="1:25" ht="17.25">
       <c r="A2" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:25">
+    <row r="3" spans="1:25" ht="15">
       <c r="B3" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:25">
+    <row r="4" spans="1:25" ht="15">
       <c r="B4" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="17.399999999999999">
+    <row r="6" spans="1:25" ht="17.25">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -5682,17 +5682,17 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="17.399999999999999">
+    <row r="12" spans="1:25" ht="17.25">
       <c r="A12" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:25">
+    <row r="13" spans="1:25" ht="15">
       <c r="B13" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="22.8">
+    <row r="14" spans="1:25" ht="23.25">
       <c r="B14" s="3" t="s">
         <v>115</v>
       </c>
@@ -5709,13 +5709,13 @@
       <c r="X14" s="19"/>
       <c r="Y14" s="20"/>
     </row>
-    <row r="15" spans="1:25" ht="17.399999999999999">
+    <row r="15" spans="1:25" ht="17.25">
       <c r="P15" s="21" t="s">
         <v>152</v>
       </c>
       <c r="Y15" s="22"/>
     </row>
-    <row r="16" spans="1:25" ht="17.399999999999999">
+    <row r="16" spans="1:25" ht="17.25">
       <c r="A16" s="2" t="s">
         <v>116</v>
       </c>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="Y16" s="22"/>
     </row>
-    <row r="17" spans="1:25">
+    <row r="17" spans="1:25" ht="15">
       <c r="B17" s="3" t="s">
         <v>117</v>
       </c>
@@ -5735,14 +5735,14 @@
       </c>
       <c r="Y17" s="22"/>
     </row>
-    <row r="18" spans="1:25">
+    <row r="18" spans="1:25" ht="15">
       <c r="P18" s="23"/>
       <c r="Q18" s="3" t="s">
         <v>155</v>
       </c>
       <c r="Y18" s="22"/>
     </row>
-    <row r="19" spans="1:25" ht="17.399999999999999">
+    <row r="19" spans="1:25" ht="17.25">
       <c r="A19" s="2" t="s">
         <v>118</v>
       </c>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="Y21" s="22"/>
     </row>
-    <row r="22" spans="1:25" ht="17.399999999999999">
+    <row r="22" spans="1:25" ht="17.25">
       <c r="B22" s="12" t="s">
         <v>121</v>
       </c>
@@ -5782,14 +5782,14 @@
       <c r="R22" s="12"/>
       <c r="Y22" s="22"/>
     </row>
-    <row r="23" spans="1:25">
+    <row r="23" spans="1:25" ht="15">
       <c r="P23" s="24"/>
       <c r="Q23" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Y23" s="22"/>
     </row>
-    <row r="24" spans="1:25" ht="22.8">
+    <row r="24" spans="1:25" ht="23.25">
       <c r="A24" s="17" t="s">
         <v>144</v>
       </c>
@@ -5799,7 +5799,7 @@
       </c>
       <c r="Y24" s="22"/>
     </row>
-    <row r="25" spans="1:25" ht="17.399999999999999">
+    <row r="25" spans="1:25" ht="17.25">
       <c r="A25" s="2" t="s">
         <v>145</v>
       </c>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Y25" s="22"/>
     </row>
-    <row r="26" spans="1:25" ht="17.399999999999999">
+    <row r="26" spans="1:25" ht="17.25">
       <c r="B26" s="2" t="s">
         <v>122</v>
       </c>
@@ -5874,7 +5874,7 @@
       <c r="X31" s="27"/>
       <c r="Y31" s="29"/>
     </row>
-    <row r="33" spans="1:16" ht="17.399999999999999">
+    <row r="33" spans="1:16" ht="17.25">
       <c r="A33" s="2" t="s">
         <v>150</v>
       </c>
@@ -5894,18 +5894,18 @@
     <row r="36" spans="1:16">
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="17.399999999999999">
+    <row r="37" spans="1:16" ht="17.25">
       <c r="A37" s="2" t="s">
         <v>146</v>
       </c>
       <c r="P37" s="12"/>
     </row>
-    <row r="38" spans="1:16" ht="17.399999999999999">
+    <row r="38" spans="1:16" ht="17.25">
       <c r="B38" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:16">
+    <row r="39" spans="1:16" ht="15">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -5915,17 +5915,17 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:16">
+    <row r="41" spans="1:16" ht="15">
       <c r="B41" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:16">
+    <row r="42" spans="1:16" ht="15">
       <c r="B42" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="17.399999999999999">
+    <row r="44" spans="1:16" ht="17.25">
       <c r="A44" s="2" t="s">
         <v>147</v>
       </c>
@@ -5950,7 +5950,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="17.399999999999999">
+    <row r="50" spans="1:2" ht="17.25">
       <c r="A50" s="2" t="s">
         <v>148</v>
       </c>
@@ -5970,12 +5970,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="17.399999999999999">
+    <row r="55" spans="1:2" ht="17.25">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" ht="15">
       <c r="B56" s="3" t="s">
         <v>141</v>
       </c>
@@ -5994,7 +5994,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="K4:Q90"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
     <row r="4" spans="12:13">
       <c r="M4" t="s">
@@ -6065,12 +6065,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R65"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="10" max="10" width="9.8984375" customWidth="1"/>
+    <col min="10" max="10" width="9.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="22.8">
+    <row r="1" spans="1:10" ht="23.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6085,18 +6085,18 @@
       <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="41" t="s">
+      <c r="E2" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41" t="s">
+      <c r="F2" s="44"/>
+      <c r="G2" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41" t="s">
+      <c r="H2" s="44"/>
+      <c r="I2" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="41"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="B3" s="8" t="s">
@@ -6108,18 +6108,18 @@
       <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43" t="s">
+      <c r="F3" s="46"/>
+      <c r="G3" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="43"/>
-      <c r="I3" s="42" t="s">
+      <c r="H3" s="46"/>
+      <c r="I3" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="42"/>
+      <c r="J3" s="45"/>
     </row>
     <row r="4" spans="1:10" ht="30.75" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -6131,18 +6131,18 @@
       <c r="D4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="43"/>
-      <c r="G4" s="43" t="s">
+      <c r="F4" s="46"/>
+      <c r="G4" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="42" t="s">
+      <c r="H4" s="46"/>
+      <c r="I4" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="42"/>
+      <c r="J4" s="45"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="B5" s="8" t="s">
@@ -6154,20 +6154,20 @@
       <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43" t="s">
+      <c r="F5" s="46"/>
+      <c r="G5" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="42" t="s">
+      <c r="H5" s="46"/>
+      <c r="I5" s="45" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="42"/>
-    </row>
-    <row r="6" spans="1:10" ht="27.6">
+      <c r="J5" s="45"/>
+    </row>
+    <row r="6" spans="1:10" ht="28.5">
       <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
@@ -6177,18 +6177,18 @@
       <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43" t="s">
+      <c r="F6" s="46"/>
+      <c r="G6" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43" t="s">
+      <c r="H6" s="46"/>
+      <c r="I6" s="46" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="43"/>
+      <c r="J6" s="46"/>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="6"/>
@@ -6201,27 +6201,27 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="22.8">
+    <row r="9" spans="1:10" ht="23.25">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17.399999999999999">
+    <row r="11" spans="1:10" ht="17.25">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" ht="15">
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" ht="15">
       <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" ht="15">
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
@@ -6231,17 +6231,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.399999999999999">
+    <row r="17" spans="1:18" ht="17.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18">
+    <row r="18" spans="1:18" ht="15">
       <c r="B18" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="22.8">
+    <row r="19" spans="1:18" ht="23.25">
       <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
@@ -6278,7 +6278,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.399999999999999">
+    <row r="24" spans="1:18" ht="17.25">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -6286,7 +6286,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" ht="15">
       <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.399999999999999">
+    <row r="29" spans="1:18" ht="17.25">
       <c r="A29" s="2" t="s">
         <v>42</v>
       </c>
@@ -6323,7 +6323,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" ht="15">
       <c r="B30" s="4" t="s">
         <v>43</v>
       </c>
@@ -6339,7 +6339,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" ht="15">
       <c r="C32" s="5" t="s">
         <v>45</v>
       </c>
@@ -6352,7 +6352,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="22.8">
+    <row r="34" spans="1:17" ht="23.25">
       <c r="B34" s="3" t="s">
         <v>47</v>
       </c>
@@ -6360,7 +6360,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:17" ht="15">
       <c r="Q35" s="3" t="s">
         <v>63</v>
       </c>
@@ -6375,15 +6375,15 @@
       <c r="D36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="41" t="s">
+      <c r="E36" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="41"/>
+      <c r="F36" s="44"/>
       <c r="Q36" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:17" ht="15">
       <c r="B37" s="8" t="s">
         <v>12</v>
       </c>
@@ -6393,10 +6393,10 @@
       <c r="D37" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="42" t="s">
+      <c r="E37" s="45" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="42"/>
+      <c r="F37" s="45"/>
       <c r="Q37" s="3" t="s">
         <v>65</v>
       </c>
@@ -6411,13 +6411,13 @@
       <c r="D38" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="42" t="s">
+      <c r="E38" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="F38" s="42"/>
+      <c r="F38" s="45"/>
       <c r="Q38" s="12"/>
     </row>
-    <row r="39" spans="1:17" ht="55.2">
+    <row r="39" spans="1:17" ht="57">
       <c r="B39" s="8" t="s">
         <v>21</v>
       </c>
@@ -6427,20 +6427,20 @@
       <c r="D39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="42" t="s">
+      <c r="E39" s="45" t="s">
         <v>73</v>
       </c>
-      <c r="F39" s="42"/>
+      <c r="F39" s="45"/>
     </row>
     <row r="40" spans="1:17">
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17" ht="21">
+    <row r="41" spans="1:17" ht="20.25">
       <c r="A41" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="22.8">
+    <row r="42" spans="1:17" ht="23.25">
       <c r="B42" s="1" t="s">
         <v>75</v>
       </c>
@@ -6448,12 +6448,12 @@
     <row r="43" spans="1:17">
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:17" ht="17.399999999999999">
+    <row r="44" spans="1:17" ht="17.25">
       <c r="B44" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:17" ht="15">
       <c r="B45" s="4" t="s">
         <v>77</v>
       </c>
@@ -6483,12 +6483,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" ht="15">
       <c r="B51" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="17.399999999999999">
+    <row r="53" spans="2:2" ht="17.25">
       <c r="B53" s="2" t="s">
         <v>84</v>
       </c>
@@ -6508,12 +6508,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.399999999999999">
+    <row r="58" spans="2:2" ht="17.25">
       <c r="B58" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="2:2">
+    <row r="59" spans="2:2" ht="15">
       <c r="B59" s="4" t="s">
         <v>89</v>
       </c>
@@ -6582,9 +6582,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y107"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
-    <row r="1" spans="1:23" ht="24.6">
+    <row r="1" spans="1:23" ht="26.25">
       <c r="A1" s="39" t="s">
         <v>188</v>
       </c>
@@ -6737,7 +6737,7 @@
       <c r="Q28" s="27"/>
       <c r="R28" s="29"/>
     </row>
-    <row r="31" spans="1:18" ht="24.6">
+    <row r="31" spans="1:18" ht="26.25">
       <c r="A31" s="39" t="s">
         <v>189</v>
       </c>

--- a/unit6_debugkernel/unit6_debugkernel.xlsx
+++ b/unit6_debugkernel/unit6_debugkernel.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{025C2717-FC52-4BC1-A7A9-4037A1D7F01B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7CFB52F-C1D9-4220-B6BF-33EF5648F6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="MucLuc" sheetId="5" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="step debug kernel" sheetId="1" r:id="rId3"/>
     <sheet name="Image, zImage, uImage, vmlinux" sheetId="2" r:id="rId4"/>
     <sheet name="driver hello.ko" sheetId="3" r:id="rId5"/>
+    <sheet name="Log debug" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="352">
   <si>
     <t>✅ Bảng phân biệt nhanh:</t>
   </si>
@@ -3241,13 +3242,1648 @@
   </si>
   <si>
     <t>driver hello.ko</t>
+  </si>
+  <si>
+    <t>* Nói về hàm perror và biến toàn cục errno:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là một biến toàn cục trong thư viện C của hệ thống Unix/Linux, chứa mã lỗi của các cuộc gọi hệ thống hoặc các hàm thư viện C.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Khi một hàm gặp lỗi (thường là một cuộc gọi hệ thống như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>open()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>read()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>write()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, v.v.), nó sẽ không trả về giá trị cụ thể để chỉ ra lỗi. Thay vào đó, hệ thống sẽ thiết lập giá trị cho </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để chỉ ra loại lỗi đã xảy ra.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Sau khi một hàm gặp lỗi, bạn có thể kiểm tra giá trị của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> để biết chính xác lỗi là gì.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Các mã lỗi trong </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là các hằng số được định nghĩa trong header file </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;errno.h&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, ví dụ như </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EIO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Input/Output error), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ENOMEM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Out of memory), </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>EBADF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Bad file descriptor), v.v.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. perror</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>perror</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là một hàm thư viện C được sử dụng để in thông báo lỗi liên quan đến </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ra màn hình. Hàm này sẽ kết hợp một chuỗi mô tả tùy chọn với thông điệp lỗi tương ứng với giá trị của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và in chúng ra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stderr</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>perror</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> thường được sử dụng sau khi một cuộc gọi hệ thống trả về lỗi để người lập trình biết được lý do lỗi.</t>
+    </r>
+  </si>
+  <si>
+    <t>Cú pháp:</t>
+  </si>
+  <si>
+    <t>void perror(const char *s);</t>
+  </si>
+  <si>
+    <r>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> là chuỗi mô tả bạn muốn thêm vào thông báo lỗi (thường là tên của hàm hoặc tên của một hoạt động mà bạn đang thực hiện).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm này sẽ in ra thông báo lỗi, bao gồm cả chuỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>s</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nếu có) và thông báo lỗi được dịch từ mã </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Ví dụ:</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Giả sử bạn đang cố mở một file và hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>open()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> gặp lỗi, sau đó bạn muốn in thông báo lỗi chi tiết.</t>
+    </r>
+  </si>
+  <si>
+    <t>#include &lt;stdio.h&gt;</t>
+  </si>
+  <si>
+    <t>#include &lt;fcntl.h&gt;   // Để sử dụng open()</t>
+  </si>
+  <si>
+    <t>#include &lt;unistd.h&gt;  // Để sử dụng close()</t>
+  </si>
+  <si>
+    <t>#include &lt;errno.h&gt;   // Để sử dụng errno</t>
+  </si>
+  <si>
+    <t>#include &lt;string.h&gt;  // Để sử dụng strerror()</t>
+  </si>
+  <si>
+    <t>int main() {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Cố mở một file không tồn tại</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    int fd = open("nonexistent_file.txt", O_RDONLY);</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // Kiểm tra xem open có gặp lỗi không</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    if (fd == -1) {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        // Sử dụng perror để in thông báo lỗi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        perror("Error opening file");</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    return 0;</t>
+  </si>
+  <si>
+    <t>}</t>
+  </si>
+  <si>
+    <t>Giải thích:</t>
+  </si>
+  <si>
+    <r>
+      <t>1. open("nonexistent_file.txt", O_RDONLY)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Hàm </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ cố mở file "nonexistent_file.txt" với chế độ chỉ đọc (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>O_RDONLY</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Vì file không tồn tại, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>open</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ trả về </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và thiết lập giá trị cho biến toàn cục </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2. perror("Error opening file")</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Sau khi phát hiện lỗi (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>fd == -1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), chúng ta gọi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perror</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>perror</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> sẽ in ra chuỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"Error opening file"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> và thông báo lỗi tương ứng với giá trị của </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, ví dụ như:</t>
+    </r>
+  </si>
+  <si>
+    <t>Error opening file: No such file or directory</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Thông báo này cho biết rằng lỗi là do file không tồn tại (lỗi </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>ENOENT</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Các mã lỗi phổ biến trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="13.5"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ENOENT</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (2)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: No such file or directory.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EACCES</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (13)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Permission denied.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>ENOMEM</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (12)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Out of memory.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EIO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (5)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Input/output error.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EBADF</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (9)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: Bad file descriptor.</t>
+    </r>
+  </si>
+  <si>
+    <t>Log debug'</t>
+  </si>
+  <si>
+    <r>
+      <t>printk(KERN_DEBUG ...)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(chỉ bật khi có DEBUG)</t>
+    </r>
+  </si>
+  <si>
+    <t>pr_debug()</t>
+  </si>
+  <si>
+    <t>printk(KERN_INFO ...)</t>
+  </si>
+  <si>
+    <t>pr_info()</t>
+  </si>
+  <si>
+    <t>printk(KERN_NOTICE ...)</t>
+  </si>
+  <si>
+    <t>pr_notice()</t>
+  </si>
+  <si>
+    <t>printk(KERN_WARNING ...)</t>
+  </si>
+  <si>
+    <t>pr_warn()</t>
+  </si>
+  <si>
+    <t>printk(KERN_ERR ...)</t>
+  </si>
+  <si>
+    <t>pr_err()</t>
+  </si>
+  <si>
+    <t>printk(KERN_CRIT ...)</t>
+  </si>
+  <si>
+    <t>pr_crit()</t>
+  </si>
+  <si>
+    <t>printk(KERN_ALERT ...)</t>
+  </si>
+  <si>
+    <t>pr_alert()</t>
+  </si>
+  <si>
+    <t>printk(KERN_EMERG ...)</t>
+  </si>
+  <si>
+    <t>pr_emerg()</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tương đương với </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>printk(KERN_...)</t>
+    </r>
+  </si>
+  <si>
+    <t>Biến thể</t>
+  </si>
+  <si>
+    <t>🔁 3. Các biến thể thân thiện hơn</t>
+  </si>
+  <si>
+    <r>
+      <t>Lưu ý:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Nếu không khai báo mức (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>KERN_...</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">), mặc định là </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>KERN_WARNING</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>Dành cho dev, không in mặc định</t>
+  </si>
+  <si>
+    <t>Debug</t>
+  </si>
+  <si>
+    <t>KERN_DEBUG</t>
+  </si>
+  <si>
+    <t>Trạng thái, log debug</t>
+  </si>
+  <si>
+    <t>Thông tin</t>
+  </si>
+  <si>
+    <t>KERN_INFO</t>
+  </si>
+  <si>
+    <t>Ví dụ: kết nối thiết bị</t>
+  </si>
+  <si>
+    <t>Thông báo</t>
+  </si>
+  <si>
+    <t>KERN_NOTICE</t>
+  </si>
+  <si>
+    <t>Cảnh báo không nghiêm trọng</t>
+  </si>
+  <si>
+    <t>Cảnh báo</t>
+  </si>
+  <si>
+    <t>KERN_WARNING</t>
+  </si>
+  <si>
+    <t>Các lỗi bình thường</t>
+  </si>
+  <si>
+    <t>Lỗi</t>
+  </si>
+  <si>
+    <t>KERN_ERR</t>
+  </si>
+  <si>
+    <t>Lỗi thiết bị hoặc hỏng phần cứng</t>
+  </si>
+  <si>
+    <t>Lỗi nghiêm trọng (critical)</t>
+  </si>
+  <si>
+    <t>KERN_CRIT</t>
+  </si>
+  <si>
+    <t>Ví dụ lỗi đĩa hoặc filesystem</t>
+  </si>
+  <si>
+    <t>Cảnh báo hệ thống cần xử lý ngay</t>
+  </si>
+  <si>
+    <t>KERN_ALERT</t>
+  </si>
+  <si>
+    <t>Hệ thống gần sập hoặc sập</t>
+  </si>
+  <si>
+    <t>Cực kỳ nghiêm trọng (panic)</t>
+  </si>
+  <si>
+    <t>KERN_EMERG</t>
+  </si>
+  <si>
+    <t>Dùng để…</t>
+  </si>
+  <si>
+    <t>Ý nghĩa</t>
+  </si>
+  <si>
+    <t>Macro</t>
+  </si>
+  <si>
+    <t>Mỗi dòng log có thể gán một mức độ ưu tiên để giúp kernel phân loại và xử lý. Mức log được định nghĩa bằng các macro:</t>
+  </si>
+  <si>
+    <r>
+      <t>🧩 2. Các mức log (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>log level</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>printk(KERN_INFO "My message: %d\n", value);</t>
+  </si>
+  <si>
+    <t>#include &lt;linux/kernel.h&gt;</t>
+  </si>
+  <si>
+    <t>"Connection timed out" – thao tác chờ thiết bị phản hồi nhưng hết thời gian</t>
+  </si>
+  <si>
+    <t>-ETIMEDOUT</t>
+  </si>
+  <si>
+    <t>🔧 1. Cú pháp cơ bản</t>
+  </si>
+  <si>
+    <t>"No space left on device" – hết chỗ để ghi dữ liệu</t>
+  </si>
+  <si>
+    <t>-ENOSPC</t>
+  </si>
+  <si>
+    <t>"No such file or directory" – file hoặc đường dẫn không tồn tại</t>
+  </si>
+  <si>
+    <t>-ENOENT</t>
+  </si>
+  <si>
+    <t>"No such device or address" – không tìm thấy thiết bị</t>
+  </si>
+  <si>
+    <t>-ENXIO</t>
+  </si>
+  <si>
+    <r>
+      <t>strerror(errno)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> nếu cần chuỗi lỗi trực tiếp</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pr_info()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pr_err()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>pr_debug()</t>
+    </r>
+  </si>
+  <si>
+    <t>Hàm thay thế phổ biến</t>
+  </si>
+  <si>
+    <t>"Operation not permitted" – không đủ quyền thực hiện thao tác</t>
+  </si>
+  <si>
+    <t>-EPERM</t>
+  </si>
+  <si>
+    <t>perror("open failed");</t>
+  </si>
+  <si>
+    <t>printk(KERN_ERR "Failed to init\n");</t>
+  </si>
+  <si>
+    <t>Ví dụ sử dụng</t>
+  </si>
+  <si>
+    <t>"No such device" – thiết bị không tồn tại</t>
+  </si>
+  <si>
+    <t>-ENODEV</t>
+  </si>
+  <si>
+    <t>Không có</t>
+  </si>
+  <si>
+    <r>
+      <t>Có (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>KERN_INFO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>KERN_ERR</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>, v.v.)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hỗ trợ mức độ log</t>
+  </si>
+  <si>
+    <t>"Out of memory" – không cấp phát được bộ nhớ</t>
+  </si>
+  <si>
+    <t>-ENOMEM</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">In chuỗi mô tả lỗi từ </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ví dụ: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>"Permission denied"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Không liên kết với </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>errno</t>
+    </r>
+  </si>
+  <si>
+    <t>Liên kết lỗi hệ thống?</t>
+  </si>
+  <si>
+    <t>"Device or resource busy" – thiết bị đang bị dùng</t>
+  </si>
+  <si>
+    <t>-EBUSY</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Mặc định in ra </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>stderr</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Dmesg buffer (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>/var/log/kern.log</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>dmesg</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Hiển thị ở đâu</t>
+  </si>
+  <si>
+    <t>"Invalid argument" – đối số truyền vào sai</t>
+  </si>
+  <si>
+    <t>-EINVAL</t>
+  </si>
+  <si>
+    <r>
+      <t>Defined trong C stdlib (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;stdio.h&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Defined trong kernel (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>&lt;linux/kernel.h&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Thư viện</t>
+  </si>
+  <si>
+    <t>"Inappropriate ioctl for device" – ioctl command không được hỗ trợ bởi thiết bị</t>
+  </si>
+  <si>
+    <t>-ENOTTY</t>
+  </si>
+  <si>
+    <t>In lỗi liên quan đến system call trong user space</t>
+  </si>
+  <si>
+    <t>In log/lỗi từ driver hoặc kernel module</t>
+  </si>
+  <si>
+    <t>Mục đích</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">"Bad address" – lỗi khi truy cập sai địa chỉ (thường do </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>copy_from_user()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> hoặc </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>copy_to_user()</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>-EFAULT</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>user space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (ứng dụng C, shell tool)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Trong </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Linux kernel space</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (driver, module)</t>
+    </r>
+  </si>
+  <si>
+    <t>Ngữ cảnh sử dụng</t>
+  </si>
+  <si>
+    <t>Giá trị</t>
+  </si>
+  <si>
+    <t>Mã lỗi</t>
+  </si>
+  <si>
+    <t>perror()</t>
+  </si>
+  <si>
+    <t>printk()</t>
+  </si>
+  <si>
+    <t>Tiêu chí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return Mã lỗi </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">🔍 So sánh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>printk()</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="163"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> vs </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>perror()</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3352,13 +4988,46 @@
       <charset val="163"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="163"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="13">
@@ -3506,7 +5175,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3593,15 +5262,62 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="3"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -5326,6 +7042,89 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>79339</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>142539</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7668695" cy="409632"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2422BB4D-CCF7-4048-9F9A-6CB9F1DC5783}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7120219" y="2466639"/>
+          <a:ext cx="7668695" cy="409632"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="7278116" cy="6820852"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE295DD3-6D22-44A7-910D-44AA4F989711}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7117080" y="2872740"/>
+          <a:ext cx="7278116" cy="6820852"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -5589,10 +7388,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A553DCEE-A8AF-4E33-86F9-F082A764823C}">
-  <dimension ref="B2:B10"/>
-  <sheetFormatPr defaultColWidth="8.75" defaultRowHeight="14.25"/>
+  <dimension ref="B2:B12"/>
+  <sheetFormatPr defaultColWidth="8.69921875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="16384" width="8.75" style="41"/>
+    <col min="1" max="16384" width="8.69921875" style="41"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:2">
@@ -5618,6 +7417,11 @@
     <row r="10" spans="2:2">
       <c r="B10" s="43" t="s">
         <v>199</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" s="43" t="s">
+        <v>246</v>
       </c>
     </row>
   </sheetData>
@@ -5627,6 +7431,7 @@
     <hyperlink ref="B6" location="'step debug kernel'!A1" display="'step debug kernel" xr:uid="{3DBD5EE6-510D-4A3A-A7E0-774CF2908B21}"/>
     <hyperlink ref="B8" location="'Image, zImage, uImage, vmlinux'!A1" display="'Image, zImage, uImage, vmlinux" xr:uid="{F5C16BDE-86FE-465F-82DE-E4053248D513}"/>
     <hyperlink ref="B10" location="'driver hello.ko'!A1" display="'driver hello.ko" xr:uid="{A1178EF8-CD32-4ADE-A188-616E0C8A2914}"/>
+    <hyperlink ref="B12" location="'Log debug'!A1" display="'Log debug'" xr:uid="{4188830B-5302-43BE-B11B-A95A6820C1DC}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5635,29 +7440,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y57"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:25" ht="23.25">
+    <row r="1" spans="1:25" ht="22.8">
       <c r="A1" s="17" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" spans="1:25" ht="17.25">
+    <row r="2" spans="1:25" ht="17.399999999999999">
       <c r="A2" s="2" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="15">
+    <row r="3" spans="1:25">
       <c r="B3" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="15">
+    <row r="4" spans="1:25">
       <c r="B4" s="3" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="17.25">
+    <row r="6" spans="1:25" ht="17.399999999999999">
       <c r="A6" s="2" t="s">
         <v>108</v>
       </c>
@@ -5682,17 +7487,17 @@
         <v>112</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="17.25">
+    <row r="12" spans="1:25" ht="17.399999999999999">
       <c r="A12" s="2" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="15">
+    <row r="13" spans="1:25">
       <c r="B13" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="23.25">
+    <row r="14" spans="1:25" ht="22.8">
       <c r="B14" s="3" t="s">
         <v>115</v>
       </c>
@@ -5709,13 +7514,13 @@
       <c r="X14" s="19"/>
       <c r="Y14" s="20"/>
     </row>
-    <row r="15" spans="1:25" ht="17.25">
+    <row r="15" spans="1:25" ht="17.399999999999999">
       <c r="P15" s="21" t="s">
         <v>152</v>
       </c>
       <c r="Y15" s="22"/>
     </row>
-    <row r="16" spans="1:25" ht="17.25">
+    <row r="16" spans="1:25" ht="17.399999999999999">
       <c r="A16" s="2" t="s">
         <v>116</v>
       </c>
@@ -5725,7 +7530,7 @@
       </c>
       <c r="Y16" s="22"/>
     </row>
-    <row r="17" spans="1:25" ht="15">
+    <row r="17" spans="1:25">
       <c r="B17" s="3" t="s">
         <v>117</v>
       </c>
@@ -5735,14 +7540,14 @@
       </c>
       <c r="Y17" s="22"/>
     </row>
-    <row r="18" spans="1:25" ht="15">
+    <row r="18" spans="1:25">
       <c r="P18" s="23"/>
       <c r="Q18" s="3" t="s">
         <v>155</v>
       </c>
       <c r="Y18" s="22"/>
     </row>
-    <row r="19" spans="1:25" ht="17.25">
+    <row r="19" spans="1:25" ht="17.399999999999999">
       <c r="A19" s="2" t="s">
         <v>118</v>
       </c>
@@ -5772,7 +7577,7 @@
       </c>
       <c r="Y21" s="22"/>
     </row>
-    <row r="22" spans="1:25" ht="17.25">
+    <row r="22" spans="1:25" ht="17.399999999999999">
       <c r="B22" s="12" t="s">
         <v>121</v>
       </c>
@@ -5782,14 +7587,14 @@
       <c r="R22" s="12"/>
       <c r="Y22" s="22"/>
     </row>
-    <row r="23" spans="1:25" ht="15">
+    <row r="23" spans="1:25">
       <c r="P23" s="24"/>
       <c r="Q23" s="3" t="s">
         <v>160</v>
       </c>
       <c r="Y23" s="22"/>
     </row>
-    <row r="24" spans="1:25" ht="23.25">
+    <row r="24" spans="1:25" ht="22.8">
       <c r="A24" s="17" t="s">
         <v>144</v>
       </c>
@@ -5799,7 +7604,7 @@
       </c>
       <c r="Y24" s="22"/>
     </row>
-    <row r="25" spans="1:25" ht="17.25">
+    <row r="25" spans="1:25" ht="17.399999999999999">
       <c r="A25" s="2" t="s">
         <v>145</v>
       </c>
@@ -5809,7 +7614,7 @@
       </c>
       <c r="Y25" s="22"/>
     </row>
-    <row r="26" spans="1:25" ht="17.25">
+    <row r="26" spans="1:25" ht="17.399999999999999">
       <c r="B26" s="2" t="s">
         <v>122</v>
       </c>
@@ -5874,7 +7679,7 @@
       <c r="X31" s="27"/>
       <c r="Y31" s="29"/>
     </row>
-    <row r="33" spans="1:16" ht="17.25">
+    <row r="33" spans="1:16" ht="17.399999999999999">
       <c r="A33" s="2" t="s">
         <v>150</v>
       </c>
@@ -5894,18 +7699,18 @@
     <row r="36" spans="1:16">
       <c r="P36" s="3"/>
     </row>
-    <row r="37" spans="1:16" ht="17.25">
+    <row r="37" spans="1:16" ht="17.399999999999999">
       <c r="A37" s="2" t="s">
         <v>146</v>
       </c>
       <c r="P37" s="12"/>
     </row>
-    <row r="38" spans="1:16" ht="17.25">
+    <row r="38" spans="1:16" ht="17.399999999999999">
       <c r="B38" s="2" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="15">
+    <row r="39" spans="1:16">
       <c r="B39" s="4" t="s">
         <v>130</v>
       </c>
@@ -5915,17 +7720,17 @@
         <v>131</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="15">
+    <row r="41" spans="1:16">
       <c r="B41" s="4" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="15">
+    <row r="42" spans="1:16">
       <c r="B42" s="4" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="17.25">
+    <row r="44" spans="1:16" ht="17.399999999999999">
       <c r="A44" s="2" t="s">
         <v>147</v>
       </c>
@@ -5950,7 +7755,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="17.25">
+    <row r="50" spans="1:2" ht="17.399999999999999">
       <c r="A50" s="2" t="s">
         <v>148</v>
       </c>
@@ -5970,12 +7775,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="17.25">
+    <row r="55" spans="1:2" ht="17.399999999999999">
       <c r="A55" s="2" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="15">
+    <row r="56" spans="1:2">
       <c r="B56" s="3" t="s">
         <v>141</v>
       </c>
@@ -5994,7 +7799,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="K4:Q90"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
     <row r="4" spans="12:13">
       <c r="M4" t="s">
@@ -6065,12 +7870,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:R65"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="10" max="10" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="9.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="23.25">
+    <row r="1" spans="1:10" ht="22.8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6085,18 +7890,18 @@
       <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="44" t="s">
+      <c r="E2" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44" t="s">
+      <c r="F2" s="50"/>
+      <c r="G2" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="J2" s="44"/>
+      <c r="J2" s="50"/>
     </row>
     <row r="3" spans="1:10" ht="30" customHeight="1">
       <c r="B3" s="8" t="s">
@@ -6108,18 +7913,18 @@
       <c r="D3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46" t="s">
+      <c r="F3" s="51"/>
+      <c r="G3" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="46"/>
-      <c r="I3" s="45" t="s">
+      <c r="H3" s="51"/>
+      <c r="I3" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="45"/>
+      <c r="J3" s="49"/>
     </row>
     <row r="4" spans="1:10" ht="30.75" customHeight="1">
       <c r="B4" s="8" t="s">
@@ -6131,18 +7936,18 @@
       <c r="D4" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="46" t="s">
+      <c r="E4" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="F4" s="51"/>
+      <c r="G4" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="45" t="s">
+      <c r="H4" s="51"/>
+      <c r="I4" s="49" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="45"/>
+      <c r="J4" s="49"/>
     </row>
     <row r="5" spans="1:10" ht="30" customHeight="1">
       <c r="B5" s="8" t="s">
@@ -6154,20 +7959,20 @@
       <c r="D5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="46" t="s">
+      <c r="E5" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46" t="s">
+      <c r="F5" s="51"/>
+      <c r="G5" s="51" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="46"/>
-      <c r="I5" s="45" t="s">
+      <c r="H5" s="51"/>
+      <c r="I5" s="49" t="s">
         <v>20</v>
       </c>
-      <c r="J5" s="45"/>
-    </row>
-    <row r="6" spans="1:10" ht="28.5">
+      <c r="J5" s="49"/>
+    </row>
+    <row r="6" spans="1:10" ht="27.6">
       <c r="B6" s="8" t="s">
         <v>21</v>
       </c>
@@ -6177,18 +7982,18 @@
       <c r="D6" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="46" t="s">
+      <c r="E6" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46" t="s">
+      <c r="F6" s="51"/>
+      <c r="G6" s="51" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46" t="s">
+      <c r="H6" s="51"/>
+      <c r="I6" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="J6" s="46"/>
+      <c r="J6" s="51"/>
     </row>
     <row r="7" spans="1:10">
       <c r="B7" s="6"/>
@@ -6201,27 +8006,27 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="9" spans="1:10" ht="23.25">
+    <row r="9" spans="1:10" ht="22.8">
       <c r="A9" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="17.25">
+    <row r="11" spans="1:10" ht="17.399999999999999">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15">
+    <row r="12" spans="1:10">
       <c r="B12" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="15">
+    <row r="13" spans="1:10">
       <c r="B13" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="15">
+    <row r="14" spans="1:10">
       <c r="B14" s="4" t="s">
         <v>30</v>
       </c>
@@ -6231,17 +8036,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="17.25">
+    <row r="17" spans="1:18" ht="17.399999999999999">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="15">
+    <row r="18" spans="1:18">
       <c r="B18" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="23.25">
+    <row r="19" spans="1:18" ht="22.8">
       <c r="B19" s="4" t="s">
         <v>34</v>
       </c>
@@ -6278,7 +8083,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="17.25">
+    <row r="24" spans="1:18" ht="17.399999999999999">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -6286,7 +8091,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="15">
+    <row r="25" spans="1:18">
       <c r="B25" s="4" t="s">
         <v>39</v>
       </c>
@@ -6315,7 +8120,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="17.25">
+    <row r="29" spans="1:18" ht="17.399999999999999">
       <c r="A29" s="2" t="s">
         <v>42</v>
       </c>
@@ -6323,7 +8128,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="15">
+    <row r="30" spans="1:18">
       <c r="B30" s="4" t="s">
         <v>43</v>
       </c>
@@ -6339,7 +8144,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15">
+    <row r="32" spans="1:18">
       <c r="C32" s="5" t="s">
         <v>45</v>
       </c>
@@ -6352,7 +8157,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="34" spans="1:17" ht="23.25">
+    <row r="34" spans="1:17" ht="22.8">
       <c r="B34" s="3" t="s">
         <v>47</v>
       </c>
@@ -6360,7 +8165,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:17" ht="15">
+    <row r="35" spans="1:17">
       <c r="Q35" s="3" t="s">
         <v>63</v>
       </c>
@@ -6375,15 +8180,15 @@
       <c r="D36" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="44" t="s">
+      <c r="E36" s="50" t="s">
         <v>69</v>
       </c>
-      <c r="F36" s="44"/>
+      <c r="F36" s="50"/>
       <c r="Q36" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:17" ht="15">
+    <row r="37" spans="1:17">
       <c r="B37" s="8" t="s">
         <v>12</v>
       </c>
@@ -6393,10 +8198,10 @@
       <c r="D37" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E37" s="45" t="s">
+      <c r="E37" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="F37" s="45"/>
+      <c r="F37" s="49"/>
       <c r="Q37" s="3" t="s">
         <v>65</v>
       </c>
@@ -6411,13 +8216,13 @@
       <c r="D38" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="F38" s="45"/>
+      <c r="F38" s="49"/>
       <c r="Q38" s="12"/>
     </row>
-    <row r="39" spans="1:17" ht="57">
+    <row r="39" spans="1:17" ht="55.2">
       <c r="B39" s="8" t="s">
         <v>21</v>
       </c>
@@ -6427,20 +8232,20 @@
       <c r="D39" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="E39" s="45" t="s">
+      <c r="E39" s="49" t="s">
         <v>73</v>
       </c>
-      <c r="F39" s="45"/>
+      <c r="F39" s="49"/>
     </row>
     <row r="40" spans="1:17">
       <c r="Q40" s="3"/>
     </row>
-    <row r="41" spans="1:17" ht="20.25">
+    <row r="41" spans="1:17" ht="21">
       <c r="A41" s="13" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="42" spans="1:17" ht="23.25">
+    <row r="42" spans="1:17" ht="22.8">
       <c r="B42" s="1" t="s">
         <v>75</v>
       </c>
@@ -6448,12 +8253,12 @@
     <row r="43" spans="1:17">
       <c r="Q43" s="3"/>
     </row>
-    <row r="44" spans="1:17" ht="17.25">
+    <row r="44" spans="1:17" ht="17.399999999999999">
       <c r="B44" s="2" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:17" ht="15">
+    <row r="45" spans="1:17">
       <c r="B45" s="4" t="s">
         <v>77</v>
       </c>
@@ -6483,12 +8288,12 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="2:2" ht="15">
+    <row r="51" spans="2:2">
       <c r="B51" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="53" spans="2:2" ht="17.25">
+    <row r="53" spans="2:2" ht="17.399999999999999">
       <c r="B53" s="2" t="s">
         <v>84</v>
       </c>
@@ -6508,12 +8313,12 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="2:2" ht="17.25">
+    <row r="58" spans="2:2" ht="17.399999999999999">
       <c r="B58" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="59" spans="2:2" ht="15">
+    <row r="59" spans="2:2">
       <c r="B59" s="4" t="s">
         <v>89</v>
       </c>
@@ -6550,6 +8355,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="G6:H6"/>
     <mergeCell ref="E37:F37"/>
     <mergeCell ref="E38:F38"/>
     <mergeCell ref="E39:F39"/>
@@ -6559,16 +8374,6 @@
     <mergeCell ref="E5:F5"/>
     <mergeCell ref="E6:F6"/>
     <mergeCell ref="E36:F36"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="I6:J6"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="Q20" r:id="rId1" display="https://github.com/u-boot/u-boot/blob/master/tools/mkimage.c" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
@@ -6582,9 +8387,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:Y107"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:23" ht="26.25">
+    <row r="1" spans="1:23" ht="24.6">
       <c r="A1" s="39" t="s">
         <v>188</v>
       </c>
@@ -6737,7 +8542,7 @@
       <c r="Q28" s="27"/>
       <c r="R28" s="29"/>
     </row>
-    <row r="31" spans="1:18" ht="26.25">
+    <row r="31" spans="1:18" ht="24.6">
       <c r="A31" s="39" t="s">
         <v>189</v>
       </c>
@@ -6809,4 +8614,967 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66A00193-0F1E-4280-89CB-B56EFD71F517}">
+  <dimension ref="A1:T101"/>
+  <sheetFormatPr defaultColWidth="2.796875" defaultRowHeight="13.8"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="15" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="B2" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="C3" s="44"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="B4" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="C4" s="44"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="C5" s="44"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="B6" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="B7" s="11" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="B8" s="14" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="B9" s="14" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="B10" s="12" t="s">
+        <v>209</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="B11" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="C11" s="46"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="B12" s="47" t="s">
+        <v>212</v>
+      </c>
+      <c r="C12" s="46"/>
+    </row>
+    <row r="13" spans="1:4" ht="17.399999999999999">
+      <c r="B13" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="B14" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="C15" s="5" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="C16" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3">
+      <c r="C17" s="5" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3">
+      <c r="C18" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3">
+      <c r="C19" s="5" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3">
+      <c r="C20" s="48"/>
+    </row>
+    <row r="21" spans="3:3">
+      <c r="C21" s="5" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3">
+      <c r="C22" s="5" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3">
+      <c r="C23" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3">
+      <c r="C24" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3">
+      <c r="C25" s="5" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3">
+      <c r="C26" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="27" spans="3:3">
+      <c r="C27" s="5" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="28" spans="3:3">
+      <c r="C28" s="5" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="29" spans="3:3">
+      <c r="C29" s="5" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="30" spans="3:3">
+      <c r="C30" s="48"/>
+    </row>
+    <row r="31" spans="3:3">
+      <c r="C31" s="5" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="32" spans="3:3">
+      <c r="C32" s="5" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" ht="17.399999999999999">
+      <c r="B34" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3">
+      <c r="B35" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3">
+      <c r="B36" s="12" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3">
+      <c r="B37" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3">
+      <c r="B38" s="11" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3">
+      <c r="B39" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3">
+      <c r="B40" s="14" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="C41" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="B42" s="12" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" ht="17.399999999999999">
+      <c r="B43" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="B44" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="B45" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="B47" s="11" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="B48" s="11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="2:20" s="52" customFormat="1"/>
+    <row r="59" spans="2:20" ht="22.8">
+      <c r="B59" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="M59" s="63" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="61" spans="2:20" ht="55.2">
+      <c r="C61" s="55" t="s">
+        <v>349</v>
+      </c>
+      <c r="D61" s="55"/>
+      <c r="E61" s="62" t="s">
+        <v>348</v>
+      </c>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62" t="s">
+        <v>347</v>
+      </c>
+      <c r="I61" s="62"/>
+      <c r="J61" s="62"/>
+      <c r="K61" s="62"/>
+      <c r="M61" s="56" t="s">
+        <v>346</v>
+      </c>
+      <c r="N61" s="56" t="s">
+        <v>345</v>
+      </c>
+      <c r="O61" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="P61" s="55"/>
+      <c r="Q61" s="55"/>
+      <c r="R61" s="55"/>
+      <c r="S61" s="55"/>
+      <c r="T61" s="55"/>
+    </row>
+    <row r="62" spans="2:20" ht="79.2">
+      <c r="C62" s="61" t="s">
+        <v>344</v>
+      </c>
+      <c r="D62" s="61"/>
+      <c r="E62" s="59" t="s">
+        <v>343</v>
+      </c>
+      <c r="F62" s="59"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="I62" s="59"/>
+      <c r="J62" s="59"/>
+      <c r="K62" s="59"/>
+      <c r="M62" s="54" t="s">
+        <v>341</v>
+      </c>
+      <c r="N62" s="60">
+        <v>-14</v>
+      </c>
+      <c r="O62" s="59" t="s">
+        <v>340</v>
+      </c>
+      <c r="P62" s="59"/>
+      <c r="Q62" s="59"/>
+      <c r="R62" s="59"/>
+      <c r="S62" s="59"/>
+      <c r="T62" s="59"/>
+    </row>
+    <row r="63" spans="2:20" ht="79.2">
+      <c r="C63" s="61" t="s">
+        <v>339</v>
+      </c>
+      <c r="D63" s="61"/>
+      <c r="E63" s="59" t="s">
+        <v>338</v>
+      </c>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59" t="s">
+        <v>337</v>
+      </c>
+      <c r="I63" s="59"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="59"/>
+      <c r="M63" s="54" t="s">
+        <v>336</v>
+      </c>
+      <c r="N63" s="60">
+        <v>-25</v>
+      </c>
+      <c r="O63" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="P63" s="59"/>
+      <c r="Q63" s="59"/>
+      <c r="R63" s="59"/>
+      <c r="S63" s="59"/>
+      <c r="T63" s="59"/>
+    </row>
+    <row r="64" spans="2:20" ht="79.2">
+      <c r="C64" s="61" t="s">
+        <v>334</v>
+      </c>
+      <c r="D64" s="61"/>
+      <c r="E64" s="59" t="s">
+        <v>333</v>
+      </c>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="I64" s="59"/>
+      <c r="J64" s="59"/>
+      <c r="K64" s="59"/>
+      <c r="M64" s="54" t="s">
+        <v>331</v>
+      </c>
+      <c r="N64" s="60">
+        <v>-22</v>
+      </c>
+      <c r="O64" s="59" t="s">
+        <v>330</v>
+      </c>
+      <c r="P64" s="59"/>
+      <c r="Q64" s="59"/>
+      <c r="R64" s="59"/>
+      <c r="S64" s="59"/>
+      <c r="T64" s="59"/>
+    </row>
+    <row r="65" spans="1:20" ht="79.2">
+      <c r="C65" s="61" t="s">
+        <v>329</v>
+      </c>
+      <c r="D65" s="61"/>
+      <c r="E65" s="59" t="s">
+        <v>328</v>
+      </c>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59" t="s">
+        <v>327</v>
+      </c>
+      <c r="I65" s="59"/>
+      <c r="J65" s="59"/>
+      <c r="K65" s="59"/>
+      <c r="M65" s="54" t="s">
+        <v>326</v>
+      </c>
+      <c r="N65" s="60">
+        <v>-16</v>
+      </c>
+      <c r="O65" s="59" t="s">
+        <v>325</v>
+      </c>
+      <c r="P65" s="59"/>
+      <c r="Q65" s="59"/>
+      <c r="R65" s="59"/>
+      <c r="S65" s="59"/>
+      <c r="T65" s="59"/>
+    </row>
+    <row r="66" spans="1:20" ht="92.4">
+      <c r="C66" s="61" t="s">
+        <v>324</v>
+      </c>
+      <c r="D66" s="61"/>
+      <c r="E66" s="59" t="s">
+        <v>323</v>
+      </c>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59" t="s">
+        <v>322</v>
+      </c>
+      <c r="I66" s="59"/>
+      <c r="J66" s="59"/>
+      <c r="K66" s="59"/>
+      <c r="M66" s="54" t="s">
+        <v>321</v>
+      </c>
+      <c r="N66" s="60">
+        <v>-12</v>
+      </c>
+      <c r="O66" s="59" t="s">
+        <v>320</v>
+      </c>
+      <c r="P66" s="59"/>
+      <c r="Q66" s="59"/>
+      <c r="R66" s="59"/>
+      <c r="S66" s="59"/>
+      <c r="T66" s="59"/>
+    </row>
+    <row r="67" spans="1:20" ht="92.4">
+      <c r="C67" s="61" t="s">
+        <v>319</v>
+      </c>
+      <c r="D67" s="61"/>
+      <c r="E67" s="59" t="s">
+        <v>318</v>
+      </c>
+      <c r="F67" s="59"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59" t="s">
+        <v>317</v>
+      </c>
+      <c r="I67" s="59"/>
+      <c r="J67" s="59"/>
+      <c r="K67" s="59"/>
+      <c r="M67" s="54" t="s">
+        <v>316</v>
+      </c>
+      <c r="N67" s="60">
+        <v>-19</v>
+      </c>
+      <c r="O67" s="59" t="s">
+        <v>315</v>
+      </c>
+      <c r="P67" s="59"/>
+      <c r="Q67" s="59"/>
+      <c r="R67" s="59"/>
+      <c r="S67" s="59"/>
+      <c r="T67" s="59"/>
+    </row>
+    <row r="68" spans="1:20" ht="79.2">
+      <c r="C68" s="61" t="s">
+        <v>314</v>
+      </c>
+      <c r="D68" s="61"/>
+      <c r="E68" s="53" t="s">
+        <v>313</v>
+      </c>
+      <c r="F68" s="53"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53" t="s">
+        <v>312</v>
+      </c>
+      <c r="I68" s="53"/>
+      <c r="J68" s="53"/>
+      <c r="K68" s="53"/>
+      <c r="M68" s="54" t="s">
+        <v>311</v>
+      </c>
+      <c r="N68" s="60">
+        <v>-1</v>
+      </c>
+      <c r="O68" s="59" t="s">
+        <v>310</v>
+      </c>
+      <c r="P68" s="59"/>
+      <c r="Q68" s="59"/>
+      <c r="R68" s="59"/>
+      <c r="S68" s="59"/>
+      <c r="T68" s="59"/>
+    </row>
+    <row r="69" spans="1:20" ht="66">
+      <c r="C69" s="61" t="s">
+        <v>309</v>
+      </c>
+      <c r="D69" s="61"/>
+      <c r="E69" s="53" t="s">
+        <v>308</v>
+      </c>
+      <c r="F69" s="53"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="53" t="s">
+        <v>307</v>
+      </c>
+      <c r="I69" s="53"/>
+      <c r="J69" s="53"/>
+      <c r="K69" s="53"/>
+      <c r="M69" s="54" t="s">
+        <v>306</v>
+      </c>
+      <c r="N69" s="60">
+        <v>-6</v>
+      </c>
+      <c r="O69" s="59" t="s">
+        <v>305</v>
+      </c>
+      <c r="P69" s="59"/>
+      <c r="Q69" s="59"/>
+      <c r="R69" s="59"/>
+      <c r="S69" s="59"/>
+      <c r="T69" s="59"/>
+    </row>
+    <row r="70" spans="1:20" ht="92.4">
+      <c r="M70" s="54" t="s">
+        <v>304</v>
+      </c>
+      <c r="N70" s="60">
+        <v>-2</v>
+      </c>
+      <c r="O70" s="59" t="s">
+        <v>303</v>
+      </c>
+      <c r="P70" s="59"/>
+      <c r="Q70" s="59"/>
+      <c r="R70" s="59"/>
+      <c r="S70" s="59"/>
+      <c r="T70" s="59"/>
+    </row>
+    <row r="71" spans="1:20" ht="92.4">
+      <c r="M71" s="54" t="s">
+        <v>302</v>
+      </c>
+      <c r="N71" s="60">
+        <v>-28</v>
+      </c>
+      <c r="O71" s="59" t="s">
+        <v>301</v>
+      </c>
+      <c r="P71" s="59"/>
+      <c r="Q71" s="59"/>
+      <c r="R71" s="59"/>
+      <c r="S71" s="59"/>
+      <c r="T71" s="59"/>
+    </row>
+    <row r="72" spans="1:20" ht="118.8">
+      <c r="A72" s="57" t="s">
+        <v>300</v>
+      </c>
+      <c r="M72" s="54" t="s">
+        <v>299</v>
+      </c>
+      <c r="N72" s="60">
+        <v>-110</v>
+      </c>
+      <c r="O72" s="59" t="s">
+        <v>298</v>
+      </c>
+      <c r="P72" s="59"/>
+      <c r="Q72" s="59"/>
+      <c r="R72" s="59"/>
+      <c r="S72" s="59"/>
+      <c r="T72" s="59"/>
+    </row>
+    <row r="73" spans="1:20">
+      <c r="A73" s="48"/>
+    </row>
+    <row r="74" spans="1:20">
+      <c r="B74" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20">
+      <c r="B75" s="5" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="76" spans="1:20" ht="22.8">
+      <c r="A76" s="57" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="77" spans="1:20">
+      <c r="B77" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="79" spans="1:20">
+      <c r="B79" s="55" t="s">
+        <v>293</v>
+      </c>
+      <c r="C79" s="55"/>
+      <c r="D79" s="55" t="s">
+        <v>292</v>
+      </c>
+      <c r="E79" s="55"/>
+      <c r="F79" s="55"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55" t="s">
+        <v>291</v>
+      </c>
+      <c r="I79" s="55"/>
+      <c r="J79" s="55"/>
+      <c r="K79" s="55"/>
+    </row>
+    <row r="80" spans="1:20">
+      <c r="B80" s="53" t="s">
+        <v>290</v>
+      </c>
+      <c r="C80" s="53"/>
+      <c r="D80" s="59" t="s">
+        <v>289</v>
+      </c>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59" t="s">
+        <v>288</v>
+      </c>
+      <c r="I80" s="59"/>
+      <c r="J80" s="59"/>
+      <c r="K80" s="59"/>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="B81" s="53" t="s">
+        <v>287</v>
+      </c>
+      <c r="C81" s="53"/>
+      <c r="D81" s="59" t="s">
+        <v>286</v>
+      </c>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59" t="s">
+        <v>285</v>
+      </c>
+      <c r="I81" s="59"/>
+      <c r="J81" s="59"/>
+      <c r="K81" s="59"/>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="B82" s="53" t="s">
+        <v>284</v>
+      </c>
+      <c r="C82" s="53"/>
+      <c r="D82" s="59" t="s">
+        <v>283</v>
+      </c>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59" t="s">
+        <v>282</v>
+      </c>
+      <c r="I82" s="59"/>
+      <c r="J82" s="59"/>
+      <c r="K82" s="59"/>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="B83" s="53" t="s">
+        <v>281</v>
+      </c>
+      <c r="C83" s="53"/>
+      <c r="D83" s="59" t="s">
+        <v>280</v>
+      </c>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59" t="s">
+        <v>279</v>
+      </c>
+      <c r="I83" s="59"/>
+      <c r="J83" s="59"/>
+      <c r="K83" s="59"/>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="B84" s="53" t="s">
+        <v>278</v>
+      </c>
+      <c r="C84" s="53"/>
+      <c r="D84" s="59" t="s">
+        <v>277</v>
+      </c>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59" t="s">
+        <v>276</v>
+      </c>
+      <c r="I84" s="59"/>
+      <c r="J84" s="59"/>
+      <c r="K84" s="59"/>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="B85" s="53" t="s">
+        <v>275</v>
+      </c>
+      <c r="C85" s="53"/>
+      <c r="D85" s="59" t="s">
+        <v>274</v>
+      </c>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59" t="s">
+        <v>273</v>
+      </c>
+      <c r="I85" s="59"/>
+      <c r="J85" s="59"/>
+      <c r="K85" s="59"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="B86" s="53" t="s">
+        <v>272</v>
+      </c>
+      <c r="C86" s="53"/>
+      <c r="D86" s="59" t="s">
+        <v>271</v>
+      </c>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59" t="s">
+        <v>270</v>
+      </c>
+      <c r="I86" s="59"/>
+      <c r="J86" s="59"/>
+      <c r="K86" s="59"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="B87" s="53" t="s">
+        <v>269</v>
+      </c>
+      <c r="C87" s="53"/>
+      <c r="D87" s="59" t="s">
+        <v>268</v>
+      </c>
+      <c r="E87" s="59"/>
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="59" t="s">
+        <v>267</v>
+      </c>
+      <c r="I87" s="59"/>
+      <c r="J87" s="59"/>
+      <c r="K87" s="59"/>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" s="3"/>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" s="58" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" ht="22.8">
+      <c r="A91" s="57" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" ht="69">
+      <c r="B93" s="56" t="s">
+        <v>264</v>
+      </c>
+      <c r="C93" s="55" t="s">
+        <v>263</v>
+      </c>
+      <c r="D93" s="55"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="55"/>
+    </row>
+    <row r="94" spans="1:11" ht="79.2">
+      <c r="B94" s="54" t="s">
+        <v>262</v>
+      </c>
+      <c r="C94" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+    </row>
+    <row r="95" spans="1:11" ht="52.8">
+      <c r="B95" s="54" t="s">
+        <v>260</v>
+      </c>
+      <c r="C95" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="D95" s="53"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="53"/>
+    </row>
+    <row r="96" spans="1:11" ht="52.8">
+      <c r="B96" s="54" t="s">
+        <v>258</v>
+      </c>
+      <c r="C96" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+    </row>
+    <row r="97" spans="2:6" ht="52.8">
+      <c r="B97" s="54" t="s">
+        <v>256</v>
+      </c>
+      <c r="C97" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="D97" s="53"/>
+      <c r="E97" s="53"/>
+      <c r="F97" s="53"/>
+    </row>
+    <row r="98" spans="2:6" ht="79.2">
+      <c r="B98" s="54" t="s">
+        <v>254</v>
+      </c>
+      <c r="C98" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="53"/>
+    </row>
+    <row r="99" spans="2:6" ht="66">
+      <c r="B99" s="54" t="s">
+        <v>252</v>
+      </c>
+      <c r="C99" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="53"/>
+    </row>
+    <row r="100" spans="2:6" ht="66">
+      <c r="B100" s="54" t="s">
+        <v>250</v>
+      </c>
+      <c r="C100" s="53" t="s">
+        <v>249</v>
+      </c>
+      <c r="D100" s="53"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="53"/>
+    </row>
+    <row r="101" spans="2:6" ht="66">
+      <c r="B101" s="54" t="s">
+        <v>248</v>
+      </c>
+      <c r="C101" s="53" t="s">
+        <v>247</v>
+      </c>
+      <c r="D101" s="53"/>
+      <c r="E101" s="53"/>
+      <c r="F101" s="53"/>
+    </row>
+  </sheetData>
+  <mergeCells count="75">
+    <mergeCell ref="E67:G67"/>
+    <mergeCell ref="C66:D66"/>
+    <mergeCell ref="C61:D61"/>
+    <mergeCell ref="C62:D62"/>
+    <mergeCell ref="C63:D63"/>
+    <mergeCell ref="C64:D64"/>
+    <mergeCell ref="C65:D65"/>
+    <mergeCell ref="H69:K69"/>
+    <mergeCell ref="C67:D67"/>
+    <mergeCell ref="C68:D68"/>
+    <mergeCell ref="C69:D69"/>
+    <mergeCell ref="E61:G61"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="H61:K61"/>
+    <mergeCell ref="H62:K62"/>
+    <mergeCell ref="H63:K63"/>
+    <mergeCell ref="H64:K64"/>
+    <mergeCell ref="H65:K65"/>
+    <mergeCell ref="H66:K66"/>
+    <mergeCell ref="H67:K67"/>
+    <mergeCell ref="H68:K68"/>
+    <mergeCell ref="H81:K81"/>
+    <mergeCell ref="H82:K82"/>
+    <mergeCell ref="D79:G79"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="B82:C82"/>
+    <mergeCell ref="D80:G80"/>
+    <mergeCell ref="D81:G81"/>
+    <mergeCell ref="D82:G82"/>
+    <mergeCell ref="C95:F95"/>
+    <mergeCell ref="C96:F96"/>
+    <mergeCell ref="D86:G86"/>
+    <mergeCell ref="D87:G87"/>
+    <mergeCell ref="B86:C86"/>
+    <mergeCell ref="B87:C87"/>
+    <mergeCell ref="B83:C83"/>
+    <mergeCell ref="D85:G85"/>
+    <mergeCell ref="H79:K79"/>
+    <mergeCell ref="H80:K80"/>
+    <mergeCell ref="C100:F100"/>
+    <mergeCell ref="C101:F101"/>
+    <mergeCell ref="H86:K86"/>
+    <mergeCell ref="H87:K87"/>
+    <mergeCell ref="C93:F93"/>
+    <mergeCell ref="C94:F94"/>
+    <mergeCell ref="C97:F97"/>
+    <mergeCell ref="C98:F98"/>
+    <mergeCell ref="C99:F99"/>
+    <mergeCell ref="H83:K83"/>
+    <mergeCell ref="H84:K84"/>
+    <mergeCell ref="H85:K85"/>
+    <mergeCell ref="B84:C84"/>
+    <mergeCell ref="B85:C85"/>
+    <mergeCell ref="D83:G83"/>
+    <mergeCell ref="D84:G84"/>
+    <mergeCell ref="O67:T67"/>
+    <mergeCell ref="O68:T68"/>
+    <mergeCell ref="O69:T69"/>
+    <mergeCell ref="O70:T70"/>
+    <mergeCell ref="O71:T71"/>
+    <mergeCell ref="O72:T72"/>
+    <mergeCell ref="O61:T61"/>
+    <mergeCell ref="O62:T62"/>
+    <mergeCell ref="O63:T63"/>
+    <mergeCell ref="O64:T64"/>
+    <mergeCell ref="O65:T65"/>
+    <mergeCell ref="O66:T66"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>